--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_metropolitana.xlsx
@@ -183,7 +183,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:39</t>
+    <t xml:space="preserve">2026-09-09 20:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_metropolitana.xlsx
@@ -24,156 +24,156 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
-    <t xml:space="preserve">El Bosque</t>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
   </si>
   <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:43</t>
+    <t xml:space="preserve">2026-09-18 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -595,7 +595,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.34</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.72</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6">
@@ -627,7 +627,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="9">
@@ -651,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.87</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="11">
@@ -667,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.7</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="12">
@@ -675,7 +675,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.94</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="14">
@@ -691,7 +691,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.58</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="15">
@@ -699,7 +699,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="16">
@@ -707,7 +707,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.05</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="17">
@@ -715,7 +715,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.97</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="18">
@@ -723,7 +723,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.94</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="19">
@@ -731,7 +731,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.18</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="21">
@@ -747,7 +747,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.27</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="22">
@@ -755,7 +755,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.67</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="23">
@@ -763,7 +763,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>4.26</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -771,7 +771,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.59</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="25">
@@ -779,7 +779,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="26">
@@ -787,7 +787,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="27">
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.9</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="28">
@@ -803,7 +803,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.92</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="29">
@@ -811,7 +811,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.46</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2.76</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="31">
@@ -827,7 +827,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.27</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="32">
@@ -835,7 +835,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3.47</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -843,7 +843,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.37</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="34">
@@ -851,7 +851,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.28</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="35">
@@ -859,7 +859,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="36">
@@ -867,7 +867,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.9</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="37">
@@ -875,7 +875,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="38">
@@ -883,7 +883,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>3.62</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="39">
@@ -891,7 +891,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="40">
@@ -899,7 +899,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="41">
@@ -907,7 +907,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="42">
@@ -915,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>3.66</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="43">
@@ -923,7 +923,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>3.21</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="44">
@@ -931,7 +931,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>3.56</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="45">
@@ -939,7 +939,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>3.02</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="46">
@@ -947,7 +947,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1.84</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="47">
@@ -955,7 +955,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1.37</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="48">
@@ -963,7 +963,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>3.97</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="49">
@@ -971,7 +971,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>2.23</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="50">
@@ -979,7 +979,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="51">
@@ -987,7 +987,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>0.7</v>
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>
